--- a/Laporan_SPPD_2025.xlsx
+++ b/Laporan_SPPD_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KULIAH UNAIR\PKL\Laporan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0B0833-13CD-4568-8D62-F26A494C361B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A0BEDBF-DCC3-4682-95CF-AFD640AB4C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7A42D6C4-D181-4152-8C3D-C818EECFD86A}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14821" uniqueCount="2476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14787" uniqueCount="2476">
   <si>
     <t>No. sppd</t>
   </si>
@@ -7471,8 +7471,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="dd\-mmm\-yyyy"/>
-    <numFmt numFmtId="169" formatCode="d\-mmm\-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\-mmm\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="d\-mmm\-yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -7558,37 +7558,37 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -7930,7 +7930,7 @@
     <col min="21" max="29" width="28.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="78" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -91813,7 +91813,7 @@
         <v>90003211</v>
       </c>
       <c r="H957" s="2" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="I957" s="2" t="s">
         <v>59</v>
@@ -91831,7 +91831,7 @@
         <v>2</v>
       </c>
       <c r="N957" s="2" t="s">
-        <v>271</v>
+        <v>508</v>
       </c>
       <c r="O957" s="2" t="s">
         <v>38</v>
@@ -91881,7 +91881,7 @@
     </row>
     <row r="958" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A958" s="2" t="s">
-        <v>2270</v>
+        <v>2281</v>
       </c>
       <c r="B958" s="2" t="s">
         <v>30</v>
@@ -91896,37 +91896,37 @@
         <v>32</v>
       </c>
       <c r="F958" s="2" t="s">
-        <v>2271</v>
+        <v>2282</v>
       </c>
       <c r="G958" s="2">
-        <v>90003211</v>
+        <v>910310140</v>
       </c>
       <c r="H958" s="2" t="s">
-        <v>2279</v>
+        <v>537</v>
       </c>
       <c r="I958" s="2" t="s">
-        <v>59</v>
+        <v>538</v>
       </c>
       <c r="J958" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="K958" s="2" t="s">
-        <v>2461</v>
+        <v>2469</v>
       </c>
       <c r="L958" s="2" t="s">
-        <v>2465</v>
+        <v>2468</v>
       </c>
       <c r="M958" s="2">
         <v>2</v>
       </c>
       <c r="N958" s="2" t="s">
-        <v>271</v>
+        <v>38</v>
       </c>
       <c r="O958" s="2" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="P958" s="2">
-        <v>5200132311</v>
+        <v>5200132411</v>
       </c>
       <c r="Q958" s="2" t="s">
         <v>1701</v>
@@ -91938,13 +91938,13 @@
         <v>41</v>
       </c>
       <c r="T958" s="2" t="s">
-        <v>1531</v>
+        <v>1464</v>
       </c>
       <c r="U958" s="4">
-        <v>600000</v>
+        <v>700000</v>
       </c>
       <c r="V958" s="4">
-        <v>600000</v>
+        <v>700000</v>
       </c>
       <c r="W958" s="4">
         <v>500000</v>
@@ -91953,16 +91953,16 @@
         <v>500000</v>
       </c>
       <c r="Y958" s="4">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="Z958" s="4">
-        <v>0</v>
+        <v>805000</v>
       </c>
       <c r="AA958" s="4">
-        <v>0</v>
+        <v>1664250</v>
       </c>
       <c r="AB958" s="4">
-        <v>0</v>
+        <v>1370500</v>
       </c>
       <c r="AC958" s="4">
         <v>1</v>
@@ -91970,13 +91970,13 @@
     </row>
     <row r="959" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A959" s="2" t="s">
-        <v>2270</v>
+        <v>2283</v>
       </c>
       <c r="B959" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C959" s="2" t="s">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D959" s="2" t="s">
         <v>32</v>
@@ -91985,37 +91985,37 @@
         <v>32</v>
       </c>
       <c r="F959" s="2" t="s">
-        <v>2271</v>
+        <v>2284</v>
       </c>
       <c r="G959" s="2">
-        <v>90003211</v>
+        <v>104584</v>
       </c>
       <c r="H959" s="2" t="s">
-        <v>2280</v>
+        <v>675</v>
       </c>
       <c r="I959" s="2" t="s">
-        <v>59</v>
+        <v>676</v>
       </c>
       <c r="J959" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="K959" s="2" t="s">
         <v>2461</v>
       </c>
       <c r="L959" s="2" t="s">
-        <v>2465</v>
+        <v>2461</v>
       </c>
       <c r="M959" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N959" s="2" t="s">
-        <v>508</v>
+        <v>38</v>
       </c>
       <c r="O959" s="2" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="P959" s="2">
-        <v>5200132311</v>
+        <v>5200132411</v>
       </c>
       <c r="Q959" s="2" t="s">
         <v>1701</v>
@@ -92027,19 +92027,19 @@
         <v>41</v>
       </c>
       <c r="T959" s="2" t="s">
-        <v>1531</v>
+        <v>1581</v>
       </c>
       <c r="U959" s="4">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="V959" s="4">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="W959" s="4">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="X959" s="4">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="Y959" s="4">
         <v>0</v>
@@ -92059,7 +92059,7 @@
     </row>
     <row r="960" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A960" s="2" t="s">
-        <v>2281</v>
+        <v>2285</v>
       </c>
       <c r="B960" s="2" t="s">
         <v>30</v>
@@ -92074,37 +92074,37 @@
         <v>32</v>
       </c>
       <c r="F960" s="2" t="s">
-        <v>2282</v>
+        <v>2286</v>
       </c>
       <c r="G960" s="2">
-        <v>910310140</v>
+        <v>800110064</v>
       </c>
       <c r="H960" s="2" t="s">
-        <v>537</v>
+        <v>1649</v>
       </c>
       <c r="I960" s="2" t="s">
-        <v>538</v>
+        <v>1650</v>
       </c>
       <c r="J960" s="2" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="K960" s="2" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="L960" s="2" t="s">
-        <v>2468</v>
+        <v>2471</v>
       </c>
       <c r="M960" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N960" s="2" t="s">
         <v>38</v>
       </c>
       <c r="O960" s="2" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="P960" s="2">
-        <v>5200132411</v>
+        <v>5200131411</v>
       </c>
       <c r="Q960" s="2" t="s">
         <v>1701</v>
@@ -92116,13 +92116,13 @@
         <v>41</v>
       </c>
       <c r="T960" s="2" t="s">
-        <v>1464</v>
+        <v>1651</v>
       </c>
       <c r="U960" s="4">
-        <v>700000</v>
+        <v>1050000</v>
       </c>
       <c r="V960" s="4">
-        <v>700000</v>
+        <v>1050000</v>
       </c>
       <c r="W960" s="4">
         <v>500000</v>
@@ -92131,16 +92131,16 @@
         <v>500000</v>
       </c>
       <c r="Y960" s="4">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="Z960" s="4">
-        <v>805000</v>
+        <v>1342000</v>
       </c>
       <c r="AA960" s="4">
-        <v>1664250</v>
+        <v>6296888</v>
       </c>
       <c r="AB960" s="4">
-        <v>1370500</v>
+        <v>4194750</v>
       </c>
       <c r="AC960" s="4">
         <v>1</v>
@@ -92148,13 +92148,13 @@
     </row>
     <row r="961" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A961" s="2" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="B961" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C961" s="2" t="s">
-        <v>140</v>
+        <v>31</v>
       </c>
       <c r="D961" s="2" t="s">
         <v>32</v>
@@ -92163,37 +92163,37 @@
         <v>32</v>
       </c>
       <c r="F961" s="2" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="G961" s="2">
-        <v>104584</v>
+        <v>760910011</v>
       </c>
       <c r="H961" s="2" t="s">
-        <v>675</v>
+        <v>1743</v>
       </c>
       <c r="I961" s="2" t="s">
-        <v>676</v>
+        <v>1710</v>
       </c>
       <c r="J961" s="2" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="K961" s="2" t="s">
-        <v>2461</v>
+        <v>2470</v>
       </c>
       <c r="L961" s="2" t="s">
-        <v>2461</v>
+        <v>2471</v>
       </c>
       <c r="M961" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N961" s="2" t="s">
         <v>38</v>
       </c>
       <c r="O961" s="2" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="P961" s="2">
-        <v>5200132411</v>
+        <v>5200131411</v>
       </c>
       <c r="Q961" s="2" t="s">
         <v>1701</v>
@@ -92205,19 +92205,19 @@
         <v>41</v>
       </c>
       <c r="T961" s="2" t="s">
-        <v>1581</v>
+        <v>1651</v>
       </c>
       <c r="U961" s="4">
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="V961" s="4">
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="W961" s="4">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="X961" s="4">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="Y961" s="4">
         <v>0</v>
@@ -92226,7 +92226,7 @@
         <v>0</v>
       </c>
       <c r="AA961" s="4">
-        <v>0</v>
+        <v>8289540</v>
       </c>
       <c r="AB961" s="4">
         <v>0</v>
@@ -92237,7 +92237,7 @@
     </row>
     <row r="962" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A962" s="2" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="B962" s="2" t="s">
         <v>30</v>
@@ -92252,25 +92252,25 @@
         <v>32</v>
       </c>
       <c r="F962" s="2" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="G962" s="2">
-        <v>800110064</v>
+        <v>930920230</v>
       </c>
       <c r="H962" s="2" t="s">
-        <v>1649</v>
+        <v>128</v>
       </c>
       <c r="I962" s="2" t="s">
-        <v>1650</v>
+        <v>129</v>
       </c>
       <c r="J962" s="2" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K962" s="2" t="s">
-        <v>2470</v>
+        <v>2467</v>
       </c>
       <c r="L962" s="2" t="s">
-        <v>2471</v>
+        <v>2468</v>
       </c>
       <c r="M962" s="2">
         <v>3</v>
@@ -92279,10 +92279,10 @@
         <v>38</v>
       </c>
       <c r="O962" s="2" t="s">
-        <v>130</v>
+        <v>37</v>
       </c>
       <c r="P962" s="2">
-        <v>5200131411</v>
+        <v>5200132411</v>
       </c>
       <c r="Q962" s="2" t="s">
         <v>1701</v>
@@ -92294,13 +92294,13 @@
         <v>41</v>
       </c>
       <c r="T962" s="2" t="s">
-        <v>1651</v>
+        <v>131</v>
       </c>
       <c r="U962" s="4">
-        <v>1050000</v>
+        <v>900000</v>
       </c>
       <c r="V962" s="4">
-        <v>1050000</v>
+        <v>900000</v>
       </c>
       <c r="W962" s="4">
         <v>500000</v>
@@ -92312,13 +92312,13 @@
         <v>1000000</v>
       </c>
       <c r="Z962" s="4">
-        <v>1342000</v>
+        <v>1131454</v>
       </c>
       <c r="AA962" s="4">
-        <v>6296888</v>
+        <v>3000000</v>
       </c>
       <c r="AB962" s="4">
-        <v>4194750</v>
+        <v>3024000</v>
       </c>
       <c r="AC962" s="4">
         <v>1</v>
@@ -92326,52 +92326,52 @@
     </row>
     <row r="963" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A963" s="2" t="s">
-        <v>2285</v>
+        <v>2289</v>
       </c>
       <c r="B963" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C963" s="2" t="s">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="D963" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E963" s="2" t="s">
-        <v>32</v>
+        <v>1079</v>
       </c>
       <c r="F963" s="2" t="s">
-        <v>2286</v>
+        <v>2290</v>
       </c>
       <c r="G963" s="2">
-        <v>760910011</v>
+        <v>34281031359</v>
       </c>
       <c r="H963" s="2" t="s">
-        <v>1743</v>
+        <v>2291</v>
       </c>
       <c r="I963" s="2" t="s">
-        <v>1710</v>
+        <v>2292</v>
       </c>
       <c r="J963" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="K963" s="2" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
       <c r="L963" s="2" t="s">
-        <v>2471</v>
+        <v>2468</v>
       </c>
       <c r="M963" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N963" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="O963" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O963" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="P963" s="2">
-        <v>5200131411</v>
+        <v>5200132311</v>
       </c>
       <c r="Q963" s="2" t="s">
         <v>1701</v>
@@ -92383,19 +92383,19 @@
         <v>41</v>
       </c>
       <c r="T963" s="2" t="s">
-        <v>1651</v>
+        <v>42</v>
       </c>
       <c r="U963" s="4">
-        <v>900000</v>
+        <v>375000</v>
       </c>
       <c r="V963" s="4">
-        <v>900000</v>
+        <v>375000</v>
       </c>
       <c r="W963" s="4">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="X963" s="4">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="Y963" s="4">
         <v>0</v>
@@ -92404,10 +92404,10 @@
         <v>0</v>
       </c>
       <c r="AA963" s="4">
-        <v>8289540</v>
+        <v>2152118</v>
       </c>
       <c r="AB963" s="4">
-        <v>0</v>
+        <v>1804452</v>
       </c>
       <c r="AC963" s="4">
         <v>1</v>
@@ -92415,7 +92415,7 @@
     </row>
     <row r="964" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A964" s="2" t="s">
-        <v>2287</v>
+        <v>2293</v>
       </c>
       <c r="B964" s="2" t="s">
         <v>30</v>
@@ -92430,37 +92430,37 @@
         <v>32</v>
       </c>
       <c r="F964" s="2" t="s">
-        <v>2288</v>
+        <v>2294</v>
       </c>
       <c r="G964" s="2">
-        <v>930920230</v>
+        <v>100845</v>
       </c>
       <c r="H964" s="2" t="s">
-        <v>128</v>
+        <v>2295</v>
       </c>
       <c r="I964" s="2" t="s">
-        <v>129</v>
+        <v>862</v>
       </c>
       <c r="J964" s="2" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="K964" s="2" t="s">
-        <v>2467</v>
+        <v>2461</v>
       </c>
       <c r="L964" s="2" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="M964" s="2">
         <v>3</v>
       </c>
       <c r="N964" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="O964" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O964" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="P964" s="2">
-        <v>5200132411</v>
+        <v>5200132311</v>
       </c>
       <c r="Q964" s="2" t="s">
         <v>1701</v>
@@ -92469,16 +92469,16 @@
         <v>40</v>
       </c>
       <c r="S964" s="2" t="s">
-        <v>41</v>
+        <v>1421</v>
       </c>
       <c r="T964" s="2" t="s">
-        <v>131</v>
+        <v>1422</v>
       </c>
       <c r="U964" s="4">
-        <v>900000</v>
+        <v>700000</v>
       </c>
       <c r="V964" s="4">
-        <v>900000</v>
+        <v>700000</v>
       </c>
       <c r="W964" s="4">
         <v>500000</v>
@@ -92487,16 +92487,16 @@
         <v>500000</v>
       </c>
       <c r="Y964" s="4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="Z964" s="4">
-        <v>1131454</v>
+        <v>0</v>
       </c>
       <c r="AA964" s="4">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="AB964" s="4">
-        <v>3024000</v>
+        <v>0</v>
       </c>
       <c r="AC964" s="4">
         <v>1</v>
@@ -92504,46 +92504,46 @@
     </row>
     <row r="965" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A965" s="2" t="s">
-        <v>2289</v>
+        <v>2296</v>
       </c>
       <c r="B965" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C965" s="2" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D965" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E965" s="2" t="s">
-        <v>1079</v>
+        <v>32</v>
       </c>
       <c r="F965" s="2" t="s">
-        <v>2290</v>
+        <v>2294</v>
       </c>
       <c r="G965" s="2">
-        <v>34281031359</v>
+        <v>100840</v>
       </c>
       <c r="H965" s="2" t="s">
-        <v>2291</v>
+        <v>2297</v>
       </c>
       <c r="I965" s="2" t="s">
-        <v>2292</v>
+        <v>2298</v>
       </c>
       <c r="J965" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K965" s="2" t="s">
-        <v>2468</v>
+        <v>2461</v>
       </c>
       <c r="L965" s="2" t="s">
-        <v>2468</v>
+        <v>2466</v>
       </c>
       <c r="M965" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N965" s="2" t="s">
-        <v>130</v>
+        <v>385</v>
       </c>
       <c r="O965" s="2" t="s">
         <v>38</v>
@@ -92558,22 +92558,22 @@
         <v>40</v>
       </c>
       <c r="S965" s="2" t="s">
-        <v>41</v>
+        <v>1421</v>
       </c>
       <c r="T965" s="2" t="s">
-        <v>42</v>
+        <v>2299</v>
       </c>
       <c r="U965" s="4">
-        <v>375000</v>
+        <v>750000</v>
       </c>
       <c r="V965" s="4">
-        <v>375000</v>
+        <v>750000</v>
       </c>
       <c r="W965" s="4">
-        <v>250000</v>
+        <v>500000</v>
       </c>
       <c r="X965" s="4">
-        <v>250000</v>
+        <v>500000</v>
       </c>
       <c r="Y965" s="4">
         <v>0</v>
@@ -92582,10 +92582,10 @@
         <v>0</v>
       </c>
       <c r="AA965" s="4">
-        <v>2152118</v>
+        <v>0</v>
       </c>
       <c r="AB965" s="4">
-        <v>1804452</v>
+        <v>0</v>
       </c>
       <c r="AC965" s="4">
         <v>1</v>
@@ -92593,7 +92593,7 @@
     </row>
     <row r="966" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A966" s="2" t="s">
-        <v>2293</v>
+        <v>2300</v>
       </c>
       <c r="B966" s="2" t="s">
         <v>30</v>
@@ -92605,40 +92605,40 @@
         <v>32</v>
       </c>
       <c r="E966" s="2" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="F966" s="2" t="s">
-        <v>2294</v>
+        <v>2301</v>
       </c>
       <c r="G966" s="2">
-        <v>100845</v>
+        <v>103886</v>
       </c>
       <c r="H966" s="2" t="s">
-        <v>2295</v>
+        <v>227</v>
       </c>
       <c r="I966" s="2" t="s">
-        <v>862</v>
+        <v>228</v>
       </c>
       <c r="J966" s="2" t="s">
-        <v>36</v>
+        <v>229</v>
       </c>
       <c r="K966" s="2" t="s">
-        <v>2461</v>
+        <v>2469</v>
       </c>
       <c r="L966" s="2" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="M966" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N966" s="2" t="s">
-        <v>385</v>
+        <v>38</v>
       </c>
       <c r="O966" s="2" t="s">
-        <v>38</v>
+        <v>2302</v>
       </c>
       <c r="P966" s="2">
-        <v>5200132311</v>
+        <v>5200133111</v>
       </c>
       <c r="Q966" s="2" t="s">
         <v>1701</v>
@@ -92647,22 +92647,22 @@
         <v>40</v>
       </c>
       <c r="S966" s="2" t="s">
-        <v>1421</v>
+        <v>41</v>
       </c>
       <c r="T966" s="2" t="s">
-        <v>1422</v>
+        <v>231</v>
       </c>
       <c r="U966" s="4">
         <v>700000</v>
       </c>
       <c r="V966" s="4">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="W966" s="4">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="X966" s="4">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="Y966" s="4">
         <v>0</v>
@@ -92682,7 +92682,7 @@
     </row>
     <row r="967" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A967" s="2" t="s">
-        <v>2296</v>
+        <v>2303</v>
       </c>
       <c r="B967" s="2" t="s">
         <v>30</v>
@@ -92697,34 +92697,34 @@
         <v>32</v>
       </c>
       <c r="F967" s="2" t="s">
-        <v>2294</v>
+        <v>2304</v>
       </c>
       <c r="G967" s="2">
-        <v>100840</v>
+        <v>790110041</v>
       </c>
       <c r="H967" s="2" t="s">
-        <v>2297</v>
+        <v>1357</v>
       </c>
       <c r="I967" s="2" t="s">
-        <v>2298</v>
+        <v>361</v>
       </c>
       <c r="J967" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K967" s="2" t="s">
-        <v>2461</v>
+        <v>2471</v>
       </c>
       <c r="L967" s="2" t="s">
-        <v>2466</v>
+        <v>2471</v>
       </c>
       <c r="M967" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N967" s="2" t="s">
-        <v>385</v>
+        <v>302</v>
       </c>
       <c r="O967" s="2" t="s">
-        <v>38</v>
+        <v>1124</v>
       </c>
       <c r="P967" s="2">
         <v>5200132311</v>
@@ -92736,22 +92736,22 @@
         <v>40</v>
       </c>
       <c r="S967" s="2" t="s">
-        <v>1421</v>
+        <v>303</v>
       </c>
       <c r="T967" s="2" t="s">
-        <v>2299</v>
+        <v>304</v>
       </c>
       <c r="U967" s="4">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="V967" s="4">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="W967" s="4">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="X967" s="4">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="Y967" s="4">
         <v>0</v>
@@ -92760,10 +92760,10 @@
         <v>0</v>
       </c>
       <c r="AA967" s="4">
-        <v>0</v>
+        <v>2675000</v>
       </c>
       <c r="AB967" s="4">
-        <v>0</v>
+        <v>2010750</v>
       </c>
       <c r="AC967" s="4">
         <v>1</v>
@@ -92771,7 +92771,7 @@
     </row>
     <row r="968" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A968" s="2" t="s">
-        <v>2300</v>
+        <v>2305</v>
       </c>
       <c r="B968" s="2" t="s">
         <v>30</v>
@@ -92783,40 +92783,40 @@
         <v>32</v>
       </c>
       <c r="E968" s="2" t="s">
-        <v>156</v>
+        <v>32</v>
       </c>
       <c r="F968" s="2" t="s">
-        <v>2301</v>
+        <v>923</v>
       </c>
       <c r="G968" s="2">
-        <v>103886</v>
+        <v>840320372</v>
       </c>
       <c r="H968" s="2" t="s">
-        <v>227</v>
+        <v>300</v>
       </c>
       <c r="I968" s="2" t="s">
-        <v>228</v>
+        <v>301</v>
       </c>
       <c r="J968" s="2" t="s">
-        <v>229</v>
+        <v>36</v>
       </c>
       <c r="K968" s="2" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="L968" s="2" t="s">
-        <v>2468</v>
+        <v>2471</v>
       </c>
       <c r="M968" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N968" s="2" t="s">
-        <v>38</v>
+        <v>302</v>
       </c>
       <c r="O968" s="2" t="s">
-        <v>2302</v>
+        <v>1566</v>
       </c>
       <c r="P968" s="2">
-        <v>5200133111</v>
+        <v>5200132311</v>
       </c>
       <c r="Q968" s="2" t="s">
         <v>1701</v>
@@ -92825,13 +92825,13 @@
         <v>40</v>
       </c>
       <c r="S968" s="2" t="s">
-        <v>41</v>
+        <v>303</v>
       </c>
       <c r="T968" s="2" t="s">
-        <v>231</v>
+        <v>304</v>
       </c>
       <c r="U968" s="4">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="V968" s="4">
         <v>0</v>
@@ -92849,10 +92849,10 @@
         <v>0</v>
       </c>
       <c r="AA968" s="4">
-        <v>0</v>
+        <v>2675000</v>
       </c>
       <c r="AB968" s="4">
-        <v>0</v>
+        <v>2010750</v>
       </c>
       <c r="AC968" s="4">
         <v>1</v>
@@ -92860,7 +92860,7 @@
     </row>
     <row r="969" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A969" s="2" t="s">
-        <v>2303</v>
+        <v>2306</v>
       </c>
       <c r="B969" s="2" t="s">
         <v>30</v>
@@ -92875,37 +92875,37 @@
         <v>32</v>
       </c>
       <c r="F969" s="2" t="s">
-        <v>2304</v>
+        <v>2307</v>
       </c>
       <c r="G969" s="2">
-        <v>790110041</v>
+        <v>90003211</v>
       </c>
       <c r="H969" s="2" t="s">
-        <v>1357</v>
+        <v>2217</v>
       </c>
       <c r="I969" s="2" t="s">
-        <v>361</v>
+        <v>59</v>
       </c>
       <c r="J969" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="K969" s="2" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="L969" s="2" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="M969" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N969" s="2" t="s">
-        <v>302</v>
+        <v>38</v>
       </c>
       <c r="O969" s="2" t="s">
-        <v>1124</v>
+        <v>103</v>
       </c>
       <c r="P969" s="2">
-        <v>5200132311</v>
+        <v>5200132411</v>
       </c>
       <c r="Q969" s="2" t="s">
         <v>1701</v>
@@ -92914,34 +92914,34 @@
         <v>40</v>
       </c>
       <c r="S969" s="2" t="s">
-        <v>303</v>
+        <v>41</v>
       </c>
       <c r="T969" s="2" t="s">
-        <v>304</v>
+        <v>138</v>
       </c>
       <c r="U969" s="4">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="V969" s="4">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="W969" s="4">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="X969" s="4">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="Y969" s="4">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="Z969" s="4">
-        <v>0</v>
+        <v>656250</v>
       </c>
       <c r="AA969" s="4">
-        <v>2675000</v>
+        <v>1361700</v>
       </c>
       <c r="AB969" s="4">
-        <v>2010750</v>
+        <v>1305000</v>
       </c>
       <c r="AC969" s="4">
         <v>1</v>
@@ -92949,7 +92949,7 @@
     </row>
     <row r="970" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A970" s="2" t="s">
-        <v>2305</v>
+        <v>2308</v>
       </c>
       <c r="B970" s="2" t="s">
         <v>30</v>
@@ -92964,37 +92964,37 @@
         <v>32</v>
       </c>
       <c r="F970" s="2" t="s">
-        <v>923</v>
+        <v>1820</v>
       </c>
       <c r="G970" s="2">
-        <v>840320372</v>
+        <v>90003211</v>
       </c>
       <c r="H970" s="2" t="s">
-        <v>300</v>
+        <v>1821</v>
       </c>
       <c r="I970" s="2" t="s">
-        <v>301</v>
+        <v>59</v>
       </c>
       <c r="J970" s="2" t="s">
-        <v>36</v>
+        <v>258</v>
       </c>
       <c r="K970" s="2" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="L970" s="2" t="s">
-        <v>2471</v>
+        <v>2469</v>
       </c>
       <c r="M970" s="2">
         <v>1</v>
       </c>
       <c r="N970" s="2" t="s">
-        <v>302</v>
+        <v>38</v>
       </c>
       <c r="O970" s="2" t="s">
-        <v>1566</v>
+        <v>1159</v>
       </c>
       <c r="P970" s="2">
-        <v>5200132311</v>
+        <v>5200133411</v>
       </c>
       <c r="Q970" s="2" t="s">
         <v>1701</v>
@@ -93003,16 +93003,16 @@
         <v>40</v>
       </c>
       <c r="S970" s="2" t="s">
-        <v>303</v>
+        <v>41</v>
       </c>
       <c r="T970" s="2" t="s">
-        <v>304</v>
+        <v>581</v>
       </c>
       <c r="U970" s="4">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="V970" s="4">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="W970" s="4">
         <v>0</v>
@@ -93027,10 +93027,10 @@
         <v>0</v>
       </c>
       <c r="AA970" s="4">
-        <v>2675000</v>
+        <v>0</v>
       </c>
       <c r="AB970" s="4">
-        <v>2010750</v>
+        <v>0</v>
       </c>
       <c r="AC970" s="4">
         <v>1</v>
@@ -93038,7 +93038,7 @@
     </row>
     <row r="971" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A971" s="2" t="s">
-        <v>2306</v>
+        <v>2309</v>
       </c>
       <c r="B971" s="2" t="s">
         <v>30</v>
@@ -93053,37 +93053,37 @@
         <v>32</v>
       </c>
       <c r="F971" s="2" t="s">
-        <v>2307</v>
+        <v>2310</v>
       </c>
       <c r="G971" s="2">
-        <v>90003211</v>
+        <v>104981</v>
       </c>
       <c r="H971" s="2" t="s">
-        <v>2217</v>
+        <v>629</v>
       </c>
       <c r="I971" s="2" t="s">
-        <v>59</v>
+        <v>630</v>
       </c>
       <c r="J971" s="2" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="K971" s="2" t="s">
-        <v>2469</v>
+        <v>2473</v>
       </c>
       <c r="L971" s="2" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="M971" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N971" s="2" t="s">
         <v>38</v>
       </c>
       <c r="O971" s="2" t="s">
-        <v>103</v>
+        <v>482</v>
       </c>
       <c r="P971" s="2">
-        <v>5200132411</v>
+        <v>5200131211</v>
       </c>
       <c r="Q971" s="2" t="s">
         <v>1701</v>
@@ -93095,31 +93095,31 @@
         <v>41</v>
       </c>
       <c r="T971" s="2" t="s">
-        <v>138</v>
+        <v>631</v>
       </c>
       <c r="U971" s="4">
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="V971" s="4">
-        <v>600000</v>
+        <v>800000</v>
       </c>
       <c r="W971" s="4">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="X971" s="4">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="Y971" s="4">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="Z971" s="4">
-        <v>656250</v>
+        <v>1570000</v>
       </c>
       <c r="AA971" s="4">
-        <v>1361700</v>
+        <v>0</v>
       </c>
       <c r="AB971" s="4">
-        <v>1305000</v>
+        <v>0</v>
       </c>
       <c r="AC971" s="4">
         <v>1</v>
@@ -93127,7 +93127,7 @@
     </row>
     <row r="972" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A972" s="2" t="s">
-        <v>2308</v>
+        <v>2311</v>
       </c>
       <c r="B972" s="2" t="s">
         <v>30</v>
@@ -93142,37 +93142,37 @@
         <v>32</v>
       </c>
       <c r="F972" s="2" t="s">
-        <v>1820</v>
+        <v>2312</v>
       </c>
       <c r="G972" s="2">
-        <v>90003211</v>
+        <v>102072</v>
       </c>
       <c r="H972" s="2" t="s">
-        <v>1821</v>
+        <v>71</v>
       </c>
       <c r="I972" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="J972" s="2" t="s">
-        <v>258</v>
+        <v>73</v>
       </c>
       <c r="K972" s="2" t="s">
-        <v>2469</v>
+        <v>2459</v>
       </c>
       <c r="L972" s="2" t="s">
-        <v>2469</v>
+        <v>2462</v>
       </c>
       <c r="M972" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N972" s="2" t="s">
         <v>38</v>
       </c>
       <c r="O972" s="2" t="s">
-        <v>1159</v>
+        <v>74</v>
       </c>
       <c r="P972" s="2">
-        <v>5200133411</v>
+        <v>5200132101</v>
       </c>
       <c r="Q972" s="2" t="s">
         <v>1701</v>
@@ -93184,13 +93184,13 @@
         <v>41</v>
       </c>
       <c r="T972" s="2" t="s">
-        <v>581</v>
+        <v>75</v>
       </c>
       <c r="U972" s="4">
-        <v>300000</v>
+        <v>2100000</v>
       </c>
       <c r="V972" s="4">
-        <v>300000</v>
+        <v>2100000</v>
       </c>
       <c r="W972" s="4">
         <v>0</v>
@@ -93199,16 +93199,16 @@
         <v>0</v>
       </c>
       <c r="Y972" s="4">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="Z972" s="4">
-        <v>0</v>
+        <v>1130000</v>
       </c>
       <c r="AA972" s="4">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="AB972" s="4">
-        <v>0</v>
+        <v>1680000</v>
       </c>
       <c r="AC972" s="4">
         <v>1</v>
@@ -93216,7 +93216,7 @@
     </row>
     <row r="973" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A973" s="2" t="s">
-        <v>2309</v>
+        <v>2313</v>
       </c>
       <c r="B973" s="2" t="s">
         <v>30</v>
@@ -93231,37 +93231,37 @@
         <v>32</v>
       </c>
       <c r="F973" s="2" t="s">
-        <v>2310</v>
+        <v>2314</v>
       </c>
       <c r="G973" s="2">
-        <v>104981</v>
+        <v>102072</v>
       </c>
       <c r="H973" s="2" t="s">
-        <v>629</v>
+        <v>71</v>
       </c>
       <c r="I973" s="2" t="s">
-        <v>630</v>
+        <v>72</v>
       </c>
       <c r="J973" s="2" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="K973" s="2" t="s">
-        <v>2473</v>
+        <v>2469</v>
       </c>
       <c r="L973" s="2" t="s">
-        <v>2474</v>
+        <v>2469</v>
       </c>
       <c r="M973" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N973" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O973" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O973" s="2" t="s">
-        <v>482</v>
-      </c>
       <c r="P973" s="2">
-        <v>5200131211</v>
+        <v>5200132311</v>
       </c>
       <c r="Q973" s="2" t="s">
         <v>1701</v>
@@ -93273,13 +93273,13 @@
         <v>41</v>
       </c>
       <c r="T973" s="2" t="s">
-        <v>631</v>
+        <v>75</v>
       </c>
       <c r="U973" s="4">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="V973" s="4">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="W973" s="4">
         <v>0</v>
@@ -93288,16 +93288,16 @@
         <v>0</v>
       </c>
       <c r="Y973" s="4">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="Z973" s="4">
-        <v>1570000</v>
+        <v>0</v>
       </c>
       <c r="AA973" s="4">
-        <v>0</v>
+        <v>1598720</v>
       </c>
       <c r="AB973" s="4">
-        <v>0</v>
+        <v>1275466</v>
       </c>
       <c r="AC973" s="4">
         <v>1</v>
@@ -93305,7 +93305,7 @@
     </row>
     <row r="974" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A974" s="2" t="s">
-        <v>2311</v>
+        <v>2315</v>
       </c>
       <c r="B974" s="2" t="s">
         <v>30</v>
@@ -93320,7 +93320,7 @@
         <v>32</v>
       </c>
       <c r="F974" s="2" t="s">
-        <v>2312</v>
+        <v>2316</v>
       </c>
       <c r="G974" s="2">
         <v>102072</v>
@@ -93335,13 +93335,13 @@
         <v>73</v>
       </c>
       <c r="K974" s="2" t="s">
-        <v>2459</v>
+        <v>2472</v>
       </c>
       <c r="L974" s="2" t="s">
-        <v>2462</v>
+        <v>2472</v>
       </c>
       <c r="M974" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N974" s="2" t="s">
         <v>38</v>
@@ -93350,7 +93350,7 @@
         <v>74</v>
       </c>
       <c r="P974" s="2">
-        <v>5200132101</v>
+        <v>5200132311</v>
       </c>
       <c r="Q974" s="2" t="s">
         <v>1701</v>
@@ -93365,10 +93365,10 @@
         <v>75</v>
       </c>
       <c r="U974" s="4">
-        <v>2100000</v>
+        <v>0</v>
       </c>
       <c r="V974" s="4">
-        <v>2100000</v>
+        <v>0</v>
       </c>
       <c r="W974" s="4">
         <v>0</v>
@@ -93377,16 +93377,16 @@
         <v>0</v>
       </c>
       <c r="Y974" s="4">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="Z974" s="4">
-        <v>1130000</v>
+        <v>0</v>
       </c>
       <c r="AA974" s="4">
-        <v>1500000</v>
+        <v>1658372</v>
       </c>
       <c r="AB974" s="4">
-        <v>1680000</v>
+        <v>2050750</v>
       </c>
       <c r="AC974" s="4">
         <v>1</v>
@@ -93394,13 +93394,13 @@
     </row>
     <row r="975" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A975" s="2" t="s">
-        <v>2313</v>
+        <v>2317</v>
       </c>
       <c r="B975" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C975" s="2" t="s">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="D975" s="2" t="s">
         <v>32</v>
@@ -93409,34 +93409,34 @@
         <v>32</v>
       </c>
       <c r="F975" s="2" t="s">
-        <v>2314</v>
+        <v>2318</v>
       </c>
       <c r="G975" s="2">
-        <v>102072</v>
+        <v>830420411</v>
       </c>
       <c r="H975" s="2" t="s">
-        <v>71</v>
+        <v>2319</v>
       </c>
       <c r="I975" s="2" t="s">
-        <v>72</v>
+        <v>2320</v>
       </c>
       <c r="J975" s="2" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="K975" s="2" t="s">
-        <v>2469</v>
+        <v>2472</v>
       </c>
       <c r="L975" s="2" t="s">
-        <v>2469</v>
+        <v>2472</v>
       </c>
       <c r="M975" s="2">
         <v>1</v>
       </c>
       <c r="N975" s="2" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="O975" s="2" t="s">
-        <v>38</v>
+        <v>167</v>
       </c>
       <c r="P975" s="2">
         <v>5200132311</v>
@@ -93448,22 +93448,22 @@
         <v>40</v>
       </c>
       <c r="S975" s="2" t="s">
-        <v>41</v>
+        <v>161</v>
       </c>
       <c r="T975" s="2" t="s">
-        <v>75</v>
+        <v>2321</v>
       </c>
       <c r="U975" s="4">
-        <v>0</v>
+        <v>325000</v>
       </c>
       <c r="V975" s="4">
-        <v>0</v>
+        <v>325000</v>
       </c>
       <c r="W975" s="4">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="X975" s="4">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="Y975" s="4">
         <v>0</v>
@@ -93472,10 +93472,10 @@
         <v>0</v>
       </c>
       <c r="AA975" s="4">
-        <v>1598720</v>
+        <v>1700000</v>
       </c>
       <c r="AB975" s="4">
-        <v>1275466</v>
+        <v>0</v>
       </c>
       <c r="AC975" s="4">
         <v>1</v>
@@ -93483,13 +93483,13 @@
     </row>
     <row r="976" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A976" s="2" t="s">
-        <v>2315</v>
+        <v>2322</v>
       </c>
       <c r="B976" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C976" s="2" t="s">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="D976" s="2" t="s">
         <v>32</v>
@@ -93498,34 +93498,34 @@
         <v>32</v>
       </c>
       <c r="F976" s="2" t="s">
-        <v>2316</v>
+        <v>2323</v>
       </c>
       <c r="G976" s="2">
-        <v>102072</v>
+        <v>34291111460</v>
       </c>
       <c r="H976" s="2" t="s">
-        <v>71</v>
+        <v>520</v>
       </c>
       <c r="I976" s="2" t="s">
-        <v>72</v>
+        <v>2324</v>
       </c>
       <c r="J976" s="2" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="K976" s="2" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="L976" s="2" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="M976" s="2">
         <v>1</v>
       </c>
       <c r="N976" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="O976" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="O976" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="P976" s="2">
         <v>5200132311</v>
@@ -93540,19 +93540,19 @@
         <v>41</v>
       </c>
       <c r="T976" s="2" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="U976" s="4">
-        <v>0</v>
+        <v>325000</v>
       </c>
       <c r="V976" s="4">
-        <v>0</v>
+        <v>325000</v>
       </c>
       <c r="W976" s="4">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="X976" s="4">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="Y976" s="4">
         <v>0</v>
@@ -93561,10 +93561,10 @@
         <v>0</v>
       </c>
       <c r="AA976" s="4">
-        <v>1658372</v>
+        <v>1500000</v>
       </c>
       <c r="AB976" s="4">
-        <v>2050750</v>
+        <v>2404500</v>
       </c>
       <c r="AC976" s="4">
         <v>1</v>
@@ -93572,13 +93572,13 @@
     </row>
     <row r="977" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A977" s="2" t="s">
-        <v>2317</v>
+        <v>2325</v>
       </c>
       <c r="B977" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C977" s="2" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D977" s="2" t="s">
         <v>32</v>
@@ -93587,34 +93587,34 @@
         <v>32</v>
       </c>
       <c r="F977" s="2" t="s">
-        <v>2318</v>
+        <v>2001</v>
       </c>
       <c r="G977" s="2">
-        <v>830420411</v>
+        <v>940820369</v>
       </c>
       <c r="H977" s="2" t="s">
-        <v>2319</v>
+        <v>158</v>
       </c>
       <c r="I977" s="2" t="s">
-        <v>2320</v>
+        <v>172</v>
       </c>
       <c r="J977" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K977" s="2" t="s">
-        <v>2472</v>
+        <v>2455</v>
       </c>
       <c r="L977" s="2" t="s">
-        <v>2472</v>
+        <v>2455</v>
       </c>
       <c r="M977" s="2">
         <v>1</v>
       </c>
       <c r="N977" s="2" t="s">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="O977" s="2" t="s">
-        <v>167</v>
+        <v>74</v>
       </c>
       <c r="P977" s="2">
         <v>5200132311</v>
@@ -93629,19 +93629,19 @@
         <v>161</v>
       </c>
       <c r="T977" s="2" t="s">
-        <v>2321</v>
+        <v>162</v>
       </c>
       <c r="U977" s="4">
-        <v>325000</v>
+        <v>300000</v>
       </c>
       <c r="V977" s="4">
-        <v>325000</v>
+        <v>300000</v>
       </c>
       <c r="W977" s="4">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="X977" s="4">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="Y977" s="4">
         <v>0</v>
@@ -93650,7 +93650,7 @@
         <v>0</v>
       </c>
       <c r="AA977" s="4">
-        <v>1700000</v>
+        <v>0</v>
       </c>
       <c r="AB977" s="4">
         <v>0</v>
@@ -93661,52 +93661,52 @@
     </row>
     <row r="978" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A978" s="2" t="s">
-        <v>2322</v>
+        <v>2326</v>
       </c>
       <c r="B978" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C978" s="2" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="D978" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E978" s="2" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="F978" s="2" t="s">
-        <v>2323</v>
+        <v>2327</v>
       </c>
       <c r="G978" s="2">
-        <v>34291111460</v>
+        <v>102072</v>
       </c>
       <c r="H978" s="2" t="s">
-        <v>520</v>
+        <v>71</v>
       </c>
       <c r="I978" s="2" t="s">
-        <v>2324</v>
+        <v>72</v>
       </c>
       <c r="J978" s="2" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="K978" s="2" t="s">
-        <v>2471</v>
+        <v>2475</v>
       </c>
       <c r="L978" s="2" t="s">
-        <v>2471</v>
+        <v>2475</v>
       </c>
       <c r="M978" s="2">
         <v>1</v>
       </c>
       <c r="N978" s="2" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="O978" s="2" t="s">
         <v>38</v>
       </c>
       <c r="P978" s="2">
-        <v>5200132311</v>
+        <v>5200132101</v>
       </c>
       <c r="Q978" s="2" t="s">
         <v>1701</v>
@@ -93718,19 +93718,19 @@
         <v>41</v>
       </c>
       <c r="T978" s="2" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="U978" s="4">
-        <v>325000</v>
+        <v>0</v>
       </c>
       <c r="V978" s="4">
-        <v>325000</v>
+        <v>0</v>
       </c>
       <c r="W978" s="4">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="X978" s="4">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="Y978" s="4">
         <v>0</v>
@@ -93739,10 +93739,10 @@
         <v>0</v>
       </c>
       <c r="AA978" s="4">
-        <v>1500000</v>
+        <v>1598720</v>
       </c>
       <c r="AB978" s="4">
-        <v>2404500</v>
+        <v>1338750</v>
       </c>
       <c r="AC978" s="4">
         <v>1</v>
@@ -93750,49 +93750,49 @@
     </row>
     <row r="979" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A979" s="2" t="s">
-        <v>2325</v>
+        <v>2328</v>
       </c>
       <c r="B979" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C979" s="2" t="s">
-        <v>31</v>
+        <v>184</v>
       </c>
       <c r="D979" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E979" s="2" t="s">
-        <v>32</v>
+        <v>2329</v>
       </c>
       <c r="F979" s="2" t="s">
-        <v>2001</v>
+        <v>2330</v>
       </c>
       <c r="G979" s="2">
-        <v>940820369</v>
+        <v>90003211</v>
       </c>
       <c r="H979" s="2" t="s">
-        <v>158</v>
+        <v>2331</v>
       </c>
       <c r="I979" s="2" t="s">
-        <v>172</v>
+        <v>59</v>
       </c>
       <c r="J979" s="2" t="s">
         <v>36</v>
       </c>
       <c r="K979" s="2" t="s">
-        <v>2455</v>
+        <v>2474</v>
       </c>
       <c r="L979" s="2" t="s">
-        <v>2455</v>
+        <v>2474</v>
       </c>
       <c r="M979" s="2">
         <v>1</v>
       </c>
       <c r="N979" s="2" t="s">
-        <v>160</v>
+        <v>832</v>
       </c>
       <c r="O979" s="2" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="P979" s="2">
         <v>5200132311</v>
@@ -93804,10 +93804,10 @@
         <v>40</v>
       </c>
       <c r="S979" s="2" t="s">
-        <v>161</v>
+        <v>41</v>
       </c>
       <c r="T979" s="2" t="s">
-        <v>162</v>
+        <v>42</v>
       </c>
       <c r="U979" s="4">
         <v>300000</v>
@@ -93816,10 +93816,10 @@
         <v>300000</v>
       </c>
       <c r="W979" s="4">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="X979" s="4">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="Y979" s="4">
         <v>0</v>
@@ -93828,7 +93828,7 @@
         <v>0</v>
       </c>
       <c r="AA979" s="4">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="AB979" s="4">
         <v>0</v>
@@ -93839,7 +93839,7 @@
     </row>
     <row r="980" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A980" s="2" t="s">
-        <v>2326</v>
+        <v>2332</v>
       </c>
       <c r="B980" s="2" t="s">
         <v>30</v>
@@ -93854,37 +93854,37 @@
         <v>156</v>
       </c>
       <c r="F980" s="2" t="s">
-        <v>2327</v>
+        <v>2333</v>
       </c>
       <c r="G980" s="2">
-        <v>102072</v>
+        <v>820720186</v>
       </c>
       <c r="H980" s="2" t="s">
-        <v>71</v>
+        <v>2334</v>
       </c>
       <c r="I980" s="2" t="s">
-        <v>72</v>
+        <v>2335</v>
       </c>
       <c r="J980" s="2" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="K980" s="2" t="s">
-        <v>2475</v>
+        <v>2468</v>
       </c>
       <c r="L980" s="2" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="M980" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N980" s="2" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="O980" s="2" t="s">
         <v>38</v>
       </c>
       <c r="P980" s="2">
-        <v>5200132101</v>
+        <v>5200132311</v>
       </c>
       <c r="Q980" s="2" t="s">
         <v>1701</v>
@@ -93893,10 +93893,10 @@
         <v>40</v>
       </c>
       <c r="S980" s="2" t="s">
-        <v>41</v>
+        <v>699</v>
       </c>
       <c r="T980" s="2" t="s">
-        <v>75</v>
+        <v>2224</v>
       </c>
       <c r="U980" s="4">
         <v>0</v>
@@ -93917,10 +93917,10 @@
         <v>0</v>
       </c>
       <c r="AA980" s="4">
-        <v>1598720</v>
+        <v>1361700</v>
       </c>
       <c r="AB980" s="4">
-        <v>1338750</v>
+        <v>0</v>
       </c>
       <c r="AC980" s="4">
         <v>1</v>
@@ -93928,7 +93928,7 @@
     </row>
     <row r="981" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A981" s="2" t="s">
-        <v>2328</v>
+        <v>2336</v>
       </c>
       <c r="B981" s="2" t="s">
         <v>30</v>
@@ -93943,13 +93943,13 @@
         <v>2329</v>
       </c>
       <c r="F981" s="2" t="s">
-        <v>2330</v>
+        <v>2337</v>
       </c>
       <c r="G981" s="2">
         <v>90003211</v>
       </c>
       <c r="H981" s="2" t="s">
-        <v>2331</v>
+        <v>2338</v>
       </c>
       <c r="I981" s="2" t="s">
         <v>59</v>
@@ -93958,19 +93958,19 @@
         <v>36</v>
       </c>
       <c r="K981" s="2" t="s">
-        <v>2474</v>
+        <v>2459</v>
       </c>
       <c r="L981" s="2" t="s">
-        <v>2474</v>
+        <v>2459</v>
       </c>
       <c r="M981" s="2">
         <v>1</v>
       </c>
       <c r="N981" s="2" t="s">
-        <v>832</v>
+        <v>208</v>
       </c>
       <c r="O981" s="2" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="P981" s="2">
         <v>5200132311</v>
@@ -94006,190 +94006,12 @@
         <v>0</v>
       </c>
       <c r="AA981" s="4">
-        <v>1500000</v>
+        <v>1943916</v>
       </c>
       <c r="AB981" s="4">
         <v>0</v>
       </c>
       <c r="AC981" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="982" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A982" s="2" t="s">
-        <v>2332</v>
-      </c>
-      <c r="B982" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C982" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D982" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E982" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F982" s="2" t="s">
-        <v>2333</v>
-      </c>
-      <c r="G982" s="2">
-        <v>820720186</v>
-      </c>
-      <c r="H982" s="2" t="s">
-        <v>2334</v>
-      </c>
-      <c r="I982" s="2" t="s">
-        <v>2335</v>
-      </c>
-      <c r="J982" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K982" s="2" t="s">
-        <v>2468</v>
-      </c>
-      <c r="L982" s="2" t="s">
-        <v>2473</v>
-      </c>
-      <c r="M982" s="2">
-        <v>3</v>
-      </c>
-      <c r="N982" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="O982" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="P982" s="2">
-        <v>5200132311</v>
-      </c>
-      <c r="Q982" s="2" t="s">
-        <v>1701</v>
-      </c>
-      <c r="R982" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="S982" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="T982" s="2" t="s">
-        <v>2224</v>
-      </c>
-      <c r="U982" s="4">
-        <v>0</v>
-      </c>
-      <c r="V982" s="4">
-        <v>0</v>
-      </c>
-      <c r="W982" s="4">
-        <v>0</v>
-      </c>
-      <c r="X982" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y982" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z982" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA982" s="4">
-        <v>1361700</v>
-      </c>
-      <c r="AB982" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC982" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="983" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="A983" s="2" t="s">
-        <v>2336</v>
-      </c>
-      <c r="B983" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C983" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D983" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E983" s="2" t="s">
-        <v>2329</v>
-      </c>
-      <c r="F983" s="2" t="s">
-        <v>2337</v>
-      </c>
-      <c r="G983" s="2">
-        <v>90003211</v>
-      </c>
-      <c r="H983" s="2" t="s">
-        <v>2338</v>
-      </c>
-      <c r="I983" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J983" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K983" s="2" t="s">
-        <v>2459</v>
-      </c>
-      <c r="L983" s="2" t="s">
-        <v>2459</v>
-      </c>
-      <c r="M983" s="2">
-        <v>1</v>
-      </c>
-      <c r="N983" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="O983" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="P983" s="2">
-        <v>5200132311</v>
-      </c>
-      <c r="Q983" s="2" t="s">
-        <v>1701</v>
-      </c>
-      <c r="R983" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="S983" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T983" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U983" s="4">
-        <v>300000</v>
-      </c>
-      <c r="V983" s="4">
-        <v>300000</v>
-      </c>
-      <c r="W983" s="4">
-        <v>250000</v>
-      </c>
-      <c r="X983" s="4">
-        <v>250000</v>
-      </c>
-      <c r="Y983" s="4">
-        <v>0</v>
-      </c>
-      <c r="Z983" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA983" s="4">
-        <v>1943916</v>
-      </c>
-      <c r="AB983" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC983" s="4">
         <v>1</v>
       </c>
     </row>
@@ -94224,7 +94046,7 @@
       <c r="AB984" s="12"/>
       <c r="AC984" s="12">
         <f>SUM(AC2:AC983)</f>
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
   </sheetData>
